--- a/reports/jobs_2026-10-05.xlsx
+++ b/reports/jobs_2026-10-05.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Intern Program - Engineering Pathways</t>
+          <t>AI Governance Arcitect</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/manchester/intern-program-engineering-pathways/33099/101556166016</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-Jersey/AI-Governance-Arcitect_SR-46463-1</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Theorem Proving Engineer</t>
+          <t>Intern Program - Engineering Pathways</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
+          <t>https://careers.arm.com/job/manchester/intern-program-engineering-pathways/33099/101556166016</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Graphics Engineer</t>
+          <t>Theorem Proving Engineer</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
+          <t>https://careers.arm.com/job/austin/theorem-proving-engineer/33099/97584421536</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
@@ -1185,12 +1185,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Arm India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Graphics Engineer</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://careers.arm.com/job/cambridge/graphics-engineer/33099/96521990288</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.arm.com/</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
@@ -1271,17 +1271,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Chargebee</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Product Launch and price new features without waiting on engineering</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/product/</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/careers/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Growth Test offers, run promotions and lift conversion</t>
+          <t>Product Launch and price new features without waiting on engineering</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://www.chargebee.com/solutions/role/growth/</t>
+          <t>https://www.chargebee.com/solutions/role/product/</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -1357,12 +1357,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Chargebee</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer 2</t>
+          <t>Growth Test offers, run promotions and lift conversion</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1375,11 +1375,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr"/>
       <c r="F21" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -1387,12 +1383,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
+          <t>https://www.chargebee.com/solutions/role/growth/</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://www.chargebee.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1409,12 +1405,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
+          <t>Implementation Engineer 2</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1424,7 +1420,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1434,7 +1430,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-705944-implementation-engineer-2</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
@@ -1456,12 +1452,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-3</t>
+          <t>Integration &amp; Customisation Engineer - 1 (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1471,7 +1467,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1481,7 +1477,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-1-php--reactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1503,7 +1499,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Integration &amp; Customisation Engineer-3</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1518,7 +1514,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1528,7 +1524,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-707788-integration--customisation-engineer3</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1550,12 +1546,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1563,7 +1559,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr"/>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>India Full-time</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 2</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1606,11 +1606,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E26" s="4" t="inlineStr"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -1618,7 +1614,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1640,7 +1636,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer - 3</t>
+          <t>Forward Deployed Engineer - 2</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1665,7 +1661,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
+          <t>https://exotel.com/about-us/careers/#op-705993-forward-deployed-engineer-2</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1687,7 +1683,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Forward Deployed Engineer - 3</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-706839-forward-deployed-engineer-3</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1734,12 +1730,12 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1781,12 +1777,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1806,7 +1802,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1828,12 +1824,12 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1853,7 +1849,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1870,17 +1866,17 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1890,7 +1886,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1900,12 +1896,12 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
@@ -1917,17 +1913,17 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Engineering Leader, Google COE</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1935,7 +1931,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -1943,12 +1943,12 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>https://fractal.ai/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
@@ -1960,12 +1960,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>GitLab India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software composition analysis</t>
+          <t>Engineering Leader, Google COE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/solutions/supply-chain/</t>
+          <t>https://fractal.ai/en-US/Careers/job/California/Principal-Consultant-Decision-Scientist-4_SR-42734-1</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>https://about.gitlab.com/jobs/all-jobs/</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
@@ -2003,17 +2003,17 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Goldman Sachs India</t>
+          <t>GitLab India</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Internships and Programs</t>
+          <t>Software composition analysis</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2029,12 +2029,12 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
+          <t>https://about.gitlab.com/solutions/supply-chain/</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/</t>
+          <t>https://about.gitlab.com/jobs/all-jobs/</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
+          <t>Internships and Programs</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
+          <t>https://www.goldmansachs.com/careers/students/programs-and-internships</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
@@ -2089,17 +2089,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Groww</t>
+          <t>Goldman Sachs India</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Video Editor Intern</t>
+          <t>Engineering Envisions, builds, and deploys industry-leading innovations that drive our business and extend boundaries.</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2107,11 +2107,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru-VTP, India</t>
-        </is>
-      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2119,12 +2115,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
+          <t>https://www.goldmansachs.com/careers/our-firm/engineering</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/groww</t>
+          <t>https://www.goldmansachs.com/careers/</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2141,7 +2137,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>YouTube &amp; Content - Internship</t>
+          <t>Video Editor Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2166,7 +2162,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4956817101</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2183,17 +2179,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>HighRadius</t>
+          <t>Groww</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Cloud Security Engineer</t>
+          <t>YouTube &amp; Content - Internship</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2203,7 +2199,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India</t>
+          <t>Bengaluru-VTP, India</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2213,12 +2209,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
+          <t>https://job-boards.eu.greenhouse.io/groww/jobs/4967486101</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/highradius</t>
+          <t>https://boards.greenhouse.io/groww</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2230,17 +2226,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Ixigo</t>
+          <t>HighRadius</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Backend Engineer (Java / .NET)</t>
+          <t>Cloud Security Engineer</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2250,7 +2246,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, in</t>
+          <t>Hyderabad, Telangana, India</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -2260,12 +2256,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
+          <t>https://www.highradius.com/about/careers-list/?gh_jid=7511618003</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/ixigo</t>
+          <t>https://boards.greenhouse.io/highradius</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -2282,12 +2278,12 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
+          <t>Backend Engineer (Java / .NET)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -2297,7 +2293,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>New Delhi, in</t>
+          <t>Bangalore, in</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -2307,7 +2303,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000152347660</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2324,17 +2320,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Lendingkart</t>
+          <t>Ixigo</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer</t>
+          <t>Research Engineer - Agent Intelligence &amp; Evaluation</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -2344,7 +2340,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>New Delhi, in</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -2354,12 +2350,12 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
+          <t>https://api.smartrecruiters.com/v1/companies/ixigo/postings/744000144034719</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/lendingkart</t>
+          <t>https://careers.smartrecruiters.com/ixigo</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
@@ -2371,17 +2367,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>LinkedIn India</t>
+          <t>Lendingkart</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Internship Opportunities</t>
+          <t>Backend Developer</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -2389,7 +2385,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2397,12 +2397,12 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/pathways-programs/internships</t>
+          <t>https://api.smartrecruiters.com/v1/companies/lendingkart/postings/82097348</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/</t>
+          <t>https://careers.smartrecruiters.com/lendingkart</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Internship Opportunities</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>https://careers.linkedin.com/Teams/Engineering</t>
+          <t>https://careers.linkedin.com/pathways-programs/internships</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2457,12 +2457,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Meesho</t>
+          <t>LinkedIn India</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Cluster Head- Last mile - Chennai</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -2475,11 +2475,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>Chennai, Tamil Nadu</t>
-        </is>
-      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2487,12 +2483,12 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
+          <t>https://careers.linkedin.com/Teams/Engineering</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho</t>
+          <t>https://careers.linkedin.com/</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
@@ -2509,7 +2505,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Trainee - Recruitment Coordinator</t>
+          <t>Cluster Head- Last mile - Chennai</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -2524,7 +2520,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Chennai, Tamil Nadu</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2534,7 +2530,7 @@
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
+          <t>https://jobs.lever.co/meesho/c84e4b2c-653a-4cf8-abd9-e70d0c5e4cd8</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -2551,12 +2547,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>MoEngage</t>
+          <t>Meesho</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>For Developers</t>
+          <t>Trainee - Recruitment Coordinator</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -2569,7 +2565,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, Karnataka</t>
+        </is>
+      </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2577,12 +2577,12 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/role/for-developers/</t>
+          <t>https://jobs.lever.co/meesho/1de2fc88-e203-4f1a-8046-55df700de4be</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>https://www.moengage.com/careers/</t>
+          <t>https://jobs.lever.co/meesho</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
@@ -2594,12 +2594,12 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>MongoDB India</t>
+          <t>MoEngage</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Engineer 3 - Business Systems</t>
+          <t>For Developers</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -2612,11 +2612,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2624,12 +2620,12 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
+          <t>https://www.moengage.com/role/for-developers/</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/mongodb</t>
+          <t>https://www.moengage.com/careers/</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -2641,17 +2637,17 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Mphasis</t>
+          <t>MongoDB India</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>TESTING</t>
+          <t>Engineer 3 - Business Systems</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2659,7 +2655,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
+          <t>https://www.mongodb.com/careers/job/?gh_jid=8122751</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>https://careers.mphasis.com/</t>
+          <t>https://boards.greenhouse.io/mongodb</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
@@ -2684,17 +2684,17 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>PTC India</t>
+          <t>Mphasis</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Learn more about PTC internships</t>
+          <t>TESTING</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2710,12 +2710,12 @@
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers/internships</t>
+          <t>https://careers.mphasis.com/home/hot-jobs/skill-search/testing-jobs.html</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>https://www.ptc.com/en/careers</t>
+          <t>https://careers.mphasis.com/</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -2727,12 +2727,12 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Paytm</t>
+          <t>PTC India</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Intern-Talent Acquisition</t>
+          <t>Learn more about PTC internships</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2745,11 +2745,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore, Karnataka</t>
-        </is>
-      </c>
+      <c r="E51" s="4" t="inlineStr"/>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2757,12 +2753,12 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
+          <t>https://www.ptc.com/en/careers/internships</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm</t>
+          <t>https://www.ptc.com/en/careers</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
@@ -2779,7 +2775,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Internship - Talent Acquisition</t>
+          <t>Intern-Talent Acquisition</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -2794,7 +2790,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -2804,7 +2800,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
+          <t>https://jobs.lever.co/paytm/9d497980-2032-440c-8bac-63fb53938acc</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
@@ -2826,7 +2822,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Bangalore</t>
+          <t>Internship - Talent Acquisition</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -2841,7 +2837,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, Karnataka</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -2851,7 +2847,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
+          <t>https://jobs.lever.co/paytm/a2f53649-1fe8-4a0d-97ee-24dab719a9e8</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -2873,7 +2869,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern - Noida</t>
+          <t>Talent Acquisition Intern - Bangalore</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -2888,7 +2884,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh</t>
+          <t>Bangalore, Karnataka</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -2898,7 +2894,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
+          <t>https://jobs.lever.co/paytm/88e8b698-8f03-4e09-9581-168f831fb3af</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
@@ -2915,17 +2911,17 @@
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Talent Acquisition Intern - Noida</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2933,7 +2929,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://jobs.lever.co/paytm/36f0fe45-a771-4f97-aac1-0a9ca1d73f18</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -2958,17 +2958,17 @@
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2976,11 +2976,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E56" s="4" t="inlineStr"/>
       <c r="F56" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -2988,12 +2984,12 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -3010,12 +3006,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -3035,7 +3031,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3057,12 +3053,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -3082,7 +3078,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
@@ -3099,17 +3095,17 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -3117,7 +3113,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
@@ -3142,12 +3142,12 @@
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>ENG Project/ Program - Intern</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -3160,11 +3160,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E60" s="4" t="inlineStr"/>
       <c r="F60" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3172,12 +3168,12 @@
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -3194,12 +3190,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Security Engineer - Identity and Access </t>
+          <t>ENG Project/ Program - Intern</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -3209,7 +3205,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -3219,7 +3215,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166514?gh_jid=8166514</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3241,12 +3237,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (CPD) - Winter Intern</t>
+          <t xml:space="preserve">Security Engineer - Identity and Access </t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3256,7 +3252,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3266,7 +3262,7 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8220011?gh_jid=8220011</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
@@ -3288,12 +3284,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - IAM</t>
+          <t>Software Engineer (CPD) - Winter Intern</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -3303,7 +3299,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Pune</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -3313,7 +3309,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166537?gh_jid=8166537</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3335,12 +3331,12 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - Winter Intern</t>
+          <t>Software Engineer - IAM</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -3350,7 +3346,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -3360,7 +3356,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.7956918?gh_jid=7956918</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3377,17 +3373,17 @@
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Software Engineer - Winter Intern</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -3397,7 +3393,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -3407,12 +3403,12 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8166523?gh_jid=8166523</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -3424,17 +3420,17 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>AI Screenplay Writer</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -3442,7 +3438,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr"/>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I66" s="4" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>AI Video Editor</t>
+          <t>AI Screenplay Writer</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NzMsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>AI Sound Designer</t>
+          <t>AI Video Editor</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTIsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>AI Sound Designer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3596,17 +3596,17 @@
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3614,11 +3614,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E70" s="4" t="inlineStr"/>
       <c r="F70" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3626,12 +3622,12 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0NTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr">
@@ -3648,12 +3644,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3673,7 +3669,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3690,17 +3686,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>SirionLabs</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Legal Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3708,7 +3704,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Gurugram, in</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/commercial-lawyer/</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://www.sirionlabs.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Infrastructure Transformation Engineer – IT</t>
+          <t>Legal Engineer</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
+          <t>https://www.sirion.ai/jobs/commercial-lawyer/</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3776,17 +3776,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>SirionLabs</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Infrastructure Transformation Engineer – IT</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3802,12 +3802,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://www.sirion.ai/jobs/infrastructure-transformation-engineer-it/</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://www.sirionlabs.com/careers/</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3819,12 +3819,12 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Stripe India</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Intern</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
@@ -3837,11 +3837,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr"/>
       <c r="F75" s="4" t="inlineStr">
         <is>
           <t>2026-10-05</t>
@@ -3849,12 +3845,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/stripe</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3866,12 +3862,12 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Thoughtworks India</t>
+          <t>Stripe India</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Developer (Vapasi) - Intern</t>
+          <t>Software Engineer, Intern</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
@@ -3881,12 +3877,12 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>1–5 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Bangalore, India</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3896,12 +3892,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
+          <t>https://stripe.com/jobs/search?gh_jid=8031833</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/thoughtworks</t>
+          <t>https://boards.greenhouse.io/stripe</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3918,7 +3914,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Software Procurement Intern</t>
+          <t>Developer (Vapasi) - Intern</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
@@ -3928,12 +3924,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1–5 years</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Gurgaon, India; Pune, India</t>
+          <t>Bangalore, India</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3943,7 +3939,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8210384?gh_jid=8210384</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -3960,17 +3956,17 @@
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Thoughtworks India</t>
         </is>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Software Procurement Intern</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3980,7 +3976,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru, in</t>
+          <t>Gurgaon, India; Pune, India</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3990,12 +3986,12 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.thoughtworks.com/careers/jobs/8236673?gh_jid=8236673</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://boards.greenhouse.io/thoughtworks</t>
         </is>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -4012,47 +4008,94 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
+          <t>Test Jerin</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
           <t>Software Engineer, Backend</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
         <is>
           <t>Bengaluru, in</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="G80" s="5" t="inlineStr">
         <is>
           <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H80" s="4" t="inlineStr">
         <is>
           <t>https://careers.smartrecruiters.com/unacademy</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr">
+      <c r="I80" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I79"/>
+  <autoFilter ref="A1:I80"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4132,6 +4175,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId77"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId79"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4251,35 +4295,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Vymo</t>
+          <t>Ather Energy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://getvymo.com/careers/</t>
+          <t>https://www.atherenergy.com/careers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://getvymo.com/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Ather Energy</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.atherenergy.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4288,18 +4312,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Blinkit</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://blinkit.com/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4308,18 +4332,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>CRED</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>https://careers.cred.club/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4328,18 +4352,18 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Capillary Technologies</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.capillarytech.com/careers/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4348,18 +4372,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Nykaa</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4368,18 +4392,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4388,18 +4412,18 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4408,38 +4432,38 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>WinZO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>https://www.winzogames.com/careers</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_NAME_NOT_RESOLVED at https://www.winzogames.com/careers
+Call log:
+  - navigating to "https://www.winzogames.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FirstCry</t>
+          <t>Zomato</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.firstcry.com/careers</t>
+          <t>https://www.zomato.com/careers</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Zomato</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>https://www.zomato.com/careers</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4448,22 +4472,42 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shiprocket</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>https://www.shiprocket.in/careers/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Pocket FM</t>
+          <t>Zoom India</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://pocketfm.com/careers</t>
+          <t>https://careers.zoom.us/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+          <t xml:space="preserve">playwright failed: Page.goto: net::ERR_CONNECTION_RESET at https://careers.zoom.us/
 Call log:
-  - navigating to "https://pocketfm.com/careers", waiting until "networkidle"
+  - navigating to "https://careers.zoom.us/", waiting until "networkidle"
 </t>
         </is>
       </c>
